--- a/budget-dashboard/public/budget.xlsx
+++ b/budget-dashboard/public/budget.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\PycharmProjects\FinancialDashboard\budget-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3576DDA7-DF6D-4CFF-93BF-A5C2AE48CF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576883E-71F0-402A-86BE-BABA29ABE483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28920" yWindow="-4215" windowWidth="24135" windowHeight="19455" xr2:uid="{AB41CCEA-6DC9-4FE2-81C8-E03C986F168A}"/>
+    <workbookView xWindow="29370" yWindow="-3525" windowWidth="25080" windowHeight="15480" xr2:uid="{AB41CCEA-6DC9-4FE2-81C8-E03C986F168A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Paycheck</t>
   </si>
@@ -93,7 +92,7 @@
     <t>Bofa2</t>
   </si>
   <si>
-    <t xml:space="preserve">Payday </t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -104,7 +103,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,8 +174,21 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF565A5D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +224,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB0FF97"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,7 +295,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1"/>
@@ -296,15 +314,23 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="7" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="7" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -649,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52283031-DB9A-4476-88C9-66DCDD796C5D}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -690,7 +716,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
-      <c r="T1" s="17"/>
+      <c r="T1" s="16"/>
       <c r="U1" s="7"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -731,10 +757,10 @@
       <c r="M2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="28"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="2" t="s">
         <v>13</v>
@@ -748,14 +774,14 @@
       <c r="T2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="U2" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="5">
-        <v>46001</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
@@ -777,58 +803,58 @@
       </c>
       <c r="I3" s="6">
         <f>S3</f>
-        <v>442.2</v>
+        <v>375.01</v>
       </c>
       <c r="J3" s="6">
         <f>Q5-F3</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="K3" s="6">
         <f>O5-H3</f>
-        <v>2548.89</v>
+        <v>327.73</v>
       </c>
       <c r="L3" s="6">
         <f>R5-G3+D3</f>
-        <v>17140.5</v>
+        <v>23950.04</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="2">
-        <v>2448.33</v>
+        <v>174.07</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="Q3" s="6">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="R3" s="2">
-        <v>16665.36</v>
+        <v>23529.919999999998</v>
       </c>
       <c r="S3" s="15">
-        <v>442.2</v>
+        <v>375.01</v>
       </c>
       <c r="T3" s="10">
         <f>O5+Q5+R5</f>
-        <v>19689.39</v>
+        <v>36277.770000000004</v>
       </c>
       <c r="U3" s="13">
         <f>S3-T3</f>
-        <v>-19247.189999999999</v>
+        <v>-35902.76</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="5">
-        <v>46002</v>
+        <v>46116</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -843,38 +869,36 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" ref="I4:I24" si="0">I3+C4-E4-F4-G4-H4</f>
-        <v>442.2</v>
+        <f>I3+C4-E4-F4-G4-H4</f>
+        <v>375.01</v>
       </c>
       <c r="J4" s="15">
-        <f t="shared" ref="J4:J24" si="1">J3-F4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <f t="shared" ref="K4:K24" si="2">K3-H4</f>
-        <v>2548.89</v>
+        <f>J3-F4</f>
+        <v>12000</v>
+      </c>
+      <c r="K4" s="15">
+        <f>K3-H4</f>
+        <v>327.73</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" ref="L4:L24" si="3">L3-G4+D4</f>
-        <v>17340.5</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>18</v>
-      </c>
+        <f>L3-G4+D4</f>
+        <v>23950.04</v>
+      </c>
+      <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="4">
-        <v>100.56</v>
+        <v>153.66</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="4">
         <v>0</v>
       </c>
       <c r="R4" s="10">
-        <v>475.14</v>
+        <v>420.12000000000262</v>
       </c>
       <c r="S4" s="6">
         <f>I4</f>
-        <v>442.2</v>
+        <v>375.01</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -882,10 +906,10 @@
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="5">
-        <v>46009</v>
+        <v>46121</v>
       </c>
       <c r="C5" s="3">
-        <v>3650</v>
+        <v>3000</v>
       </c>
       <c r="D5" s="4">
         <v>200</v>
@@ -899,45 +923,43 @@
       <c r="G5" s="2">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
+      <c r="H5" s="9">
+        <v>174.07</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="0"/>
-        <v>4092.2</v>
+        <f>I4+C5-E5-F5-G5-H5</f>
+        <v>3200.94</v>
       </c>
       <c r="J5" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <f t="shared" si="2"/>
-        <v>2548.89</v>
+        <f>J4-F5</f>
+        <v>12000</v>
+      </c>
+      <c r="K5" s="15">
+        <f>K4-H5</f>
+        <v>153.66000000000003</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="3"/>
-        <v>17540.5</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>7</v>
-      </c>
+        <f>L4-G5+D5</f>
+        <v>24150.04</v>
+      </c>
+      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2">
         <f>O3+O4</f>
-        <v>2548.89</v>
+        <v>327.73</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="6">
         <f>SUM(Q3:Q4)</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="R5" s="2">
-        <f t="shared" ref="R5" si="4">SUM(R3:R4)</f>
-        <v>17140.5</v>
+        <f>SUM(R3:R4)</f>
+        <v>23950.04</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" ref="S5:S25" si="5">I5</f>
-        <v>4092.2</v>
+        <f>I5</f>
+        <v>3200.94</v>
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -945,16 +967,16 @@
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="5">
-        <v>46014</v>
+        <v>46128</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1760</v>
+        <v>200</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -966,20 +988,20 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="0"/>
-        <v>2332.1999999999998</v>
+        <f>I5+C6-E6-F6-G6-H6</f>
+        <v>3200.94</v>
       </c>
       <c r="J6" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <f t="shared" si="2"/>
-        <v>2548.89</v>
+        <f>J5-F6</f>
+        <v>12000</v>
+      </c>
+      <c r="K6" s="15">
+        <f>K5-H6</f>
+        <v>153.66000000000003</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="3"/>
-        <v>17540.5</v>
+        <f>L5-G6+D6</f>
+        <v>24350.04</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -988,19 +1010,21 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="6">
-        <f t="shared" si="5"/>
-        <v>2332.1999999999998</v>
-      </c>
-      <c r="T6" s="2"/>
+        <f>I6</f>
+        <v>3200.94</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="5">
-        <v>46016</v>
+        <v>46135</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D7" s="4">
         <v>200</v>
@@ -1018,125 +1042,123 @@
         <v>0</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="0"/>
-        <v>2332.1999999999998</v>
+        <f>I6+C7-E7-F7-G7-H7</f>
+        <v>6200.9400000000005</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <f t="shared" si="2"/>
-        <v>2548.89</v>
+        <f>J6-F7</f>
+        <v>12000</v>
+      </c>
+      <c r="K7" s="15">
+        <f>K6-H7</f>
+        <v>153.66000000000003</v>
       </c>
       <c r="L7" s="6">
-        <f t="shared" si="3"/>
-        <v>17740.5</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="7">
-        <v>791.26</v>
+        <f>L6-G7+D7</f>
+        <v>24550.04</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="9">
+        <v>174.07</v>
       </c>
       <c r="O7" s="4">
-        <f>SUM(D3:D7)</f>
-        <v>600</v>
+        <f>SUM(D3:D8)</f>
+        <v>800</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="11">
-        <v>0</v>
+        <v>9504</v>
       </c>
       <c r="R7" s="11">
-        <v>15008.09</v>
+        <v>22125.73</v>
       </c>
       <c r="S7" s="6">
-        <f t="shared" si="5"/>
-        <v>2332.1999999999998</v>
+        <f>I7</f>
+        <v>6200.9400000000005</v>
       </c>
       <c r="T7" s="10">
         <f>N7+Q7+R7</f>
-        <v>15799.35</v>
+        <v>31803.8</v>
       </c>
       <c r="U7" s="13">
         <f>S7-T7</f>
-        <v>-13467.150000000001</v>
+        <v>-25602.86</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="5">
-        <v>46023</v>
+        <v>46142</v>
       </c>
       <c r="C8" s="3">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
         <v>200</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>4000</v>
-      </c>
-      <c r="H8" s="9">
-        <v>929.91999999999973</v>
+      <c r="E8" s="4">
+        <v>1938</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="0"/>
-        <v>1052.2800000000002</v>
+        <f>I7+C8-E8-F8-G8-H8</f>
+        <v>4262.9400000000005</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J7-F8</f>
+        <v>12000</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K7-H8</f>
+        <v>153.66000000000003</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="3"/>
-        <v>13940.5</v>
+        <f>L7-G8+D8</f>
+        <v>24750.04</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="9">
-        <f>N7-H7</f>
-        <v>791.26</v>
+        <f>N7-H5</f>
+        <v>0</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="11">
-        <f>Q7-F7</f>
-        <v>0</v>
+        <f>Q7-F5</f>
+        <v>9504</v>
       </c>
       <c r="R8" s="11">
-        <f>R7-G7</f>
-        <v>15008.09</v>
+        <f>R7-G5</f>
+        <v>22125.73</v>
       </c>
       <c r="S8" s="6">
-        <f t="shared" si="5"/>
-        <v>1052.2800000000002</v>
+        <f>I8</f>
+        <v>4262.9400000000005</v>
       </c>
       <c r="T8" s="10">
         <f>N8+Q8+R8</f>
-        <v>15799.35</v>
+        <v>31629.73</v>
       </c>
       <c r="U8" s="13">
         <f>S8-T8</f>
-        <v>-14747.07</v>
+        <v>-27366.79</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="5">
-        <v>46030</v>
+        <v>46149</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D9" s="4">
         <v>200</v>
@@ -1144,42 +1166,40 @@
       <c r="E9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>153.66000000000003</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="0"/>
-        <v>1052.2800000000002</v>
+        <f>I8+C9-E9-F9-G9-H9</f>
+        <v>7109.2800000000007</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J8-F9</f>
+        <v>12000</v>
       </c>
       <c r="K9" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K8-H9</f>
+        <v>0</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="3"/>
-        <v>14140.5</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>18</v>
-      </c>
+        <f>L8-G9+D9</f>
+        <v>24950.04</v>
+      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="6">
-        <f t="shared" si="5"/>
-        <v>1052.2800000000002</v>
+        <f>I9</f>
+        <v>7109.2800000000007</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -1187,10 +1207,10 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="5">
-        <v>46037</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3650</v>
+        <v>46156</v>
+      </c>
+      <c r="C10" s="20">
+        <v>0</v>
       </c>
       <c r="D10" s="4">
         <v>200</v>
@@ -1208,20 +1228,20 @@
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="0"/>
-        <v>4702.2800000000007</v>
+        <f>I9+C10-E10-F10-G10-H10</f>
+        <v>7109.2800000000007</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J9-F10</f>
+        <v>12000</v>
       </c>
       <c r="K10" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K9-H10</f>
+        <v>0</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="3"/>
-        <v>14340.5</v>
+        <f>L9-G10+D10</f>
+        <v>25150.04</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1230,8 +1250,8 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="6">
-        <f t="shared" si="5"/>
-        <v>4702.2800000000007</v>
+        <f>I10</f>
+        <v>7109.2800000000007</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -1239,10 +1259,10 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="5">
-        <v>46044</v>
+        <v>46163</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D11" s="4">
         <v>200</v>
@@ -1260,32 +1280,30 @@
         <v>0</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="0"/>
-        <v>4702.2800000000007</v>
+        <f>I10+C11-E11-F11-G11-H11</f>
+        <v>10959.28</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J10-F11</f>
+        <v>12000</v>
       </c>
       <c r="K11" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K10-H11</f>
+        <v>0</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="3"/>
-        <v>14540.5</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>7</v>
-      </c>
+        <f>L10-G11+D11</f>
+        <v>25350.04</v>
+      </c>
+      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="6">
-        <f t="shared" si="5"/>
-        <v>4702.2800000000007</v>
+        <f>I11</f>
+        <v>10959.28</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -1293,16 +1311,16 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="5">
-        <v>46045</v>
+        <v>46170</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1760</v>
+        <v>200</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1314,32 +1332,42 @@
         <v>0</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="0"/>
-        <v>2942.2800000000007</v>
+        <f>I11+C12-E12-F12-G12-H12</f>
+        <v>10959.28</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J11-F12</f>
+        <v>12000</v>
       </c>
       <c r="K12" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K11-H12</f>
+        <v>0</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="3"/>
-        <v>14540.5</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <f>L11-G12+D12</f>
+        <v>25550.04</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="11">
+        <f>N8 + (O5-N7)</f>
+        <v>153.66000000000003</v>
+      </c>
+      <c r="O12" s="4">
+        <f>SUM(D9:D13)</f>
+        <v>800</v>
+      </c>
       <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
+      <c r="Q12" s="11">
+        <f>Q8 + (Q5-Q7)</f>
+        <v>12000</v>
+      </c>
+      <c r="R12" s="11">
+        <f>R8 + (R5-R7) + O7</f>
+        <v>24750.04</v>
+      </c>
       <c r="S12" s="6">
-        <f t="shared" si="5"/>
-        <v>2942.2800000000007</v>
+        <f>I12</f>
+        <v>10959.28</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -1347,16 +1375,16 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="5">
-        <v>46051</v>
+        <v>46172</v>
       </c>
       <c r="C13" s="3">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
-        <v>200</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1938</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1368,59 +1396,56 @@
         <v>0</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="0"/>
-        <v>6592.2800000000007</v>
+        <f>I12+C13-E13-F13-G13-H13</f>
+        <v>9021.2800000000007</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J12-F13</f>
+        <v>12000</v>
       </c>
       <c r="K13" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K12-H13</f>
+        <v>0</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="3"/>
-        <v>14740.5</v>
+        <f>L12-G13+D13</f>
+        <v>25550.04</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="11">
-        <f>N8 + (O5-N7)</f>
-        <v>2548.89</v>
-      </c>
-      <c r="O13" s="4">
-        <f>SUM(D8:D12)</f>
-        <v>800</v>
-      </c>
+      <c r="N13" s="18">
+        <f>N12-H9</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="11">
-        <f>Q8 + (Q5-Q7)</f>
-        <v>0</v>
+        <f>Q12-F10</f>
+        <v>12000</v>
       </c>
       <c r="R13" s="11">
-        <f>R8 + (R5-R7) + O7</f>
-        <v>17740.5</v>
+        <f>R12-G10</f>
+        <v>24750.04</v>
       </c>
       <c r="S13" s="6">
-        <f t="shared" si="5"/>
-        <v>6592.2800000000007</v>
+        <f>I13</f>
+        <v>9021.2800000000007</v>
       </c>
       <c r="T13" s="10">
-        <f>N13+Q13+R13</f>
-        <v>20289.39</v>
+        <f>N12+Q12+R12</f>
+        <v>36903.699999999997</v>
       </c>
       <c r="U13" s="13">
         <f>S13-T13</f>
-        <v>-13697.109999999999</v>
+        <v>-27882.42</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="5">
-        <v>46058</v>
+        <v>46177</v>
       </c>
       <c r="C14" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D14" s="4">
         <v>200</v>
@@ -1429,68 +1454,56 @@
         <v>0</v>
       </c>
       <c r="F14" s="12">
-        <f>Q13</f>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="0"/>
-        <v>1592.2800000000007</v>
+        <f>I13+C14-E14-F14-G14-H14</f>
+        <v>12869.28</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J13-F14</f>
+        <v>12000</v>
       </c>
       <c r="K14" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K13-H14</f>
+        <v>0</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="3"/>
-        <v>9940.5</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="19">
-        <f>N13-H12</f>
-        <v>2548.89</v>
-      </c>
+        <f>L13-G14+D14</f>
+        <v>25748.04</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="16">
-        <f>Q13-F12</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <f>R13-G12</f>
-        <v>17740.5</v>
-      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="6">
-        <f t="shared" si="5"/>
-        <v>1592.2800000000007</v>
+        <f>I14</f>
+        <v>12869.28</v>
       </c>
       <c r="T14" s="10">
-        <f>N14+Q14+R14</f>
-        <v>20289.39</v>
+        <f>N13+Q13+R13</f>
+        <v>36750.04</v>
       </c>
       <c r="U14" s="13">
         <f>S14-T14</f>
-        <v>-18697.11</v>
+        <v>-23880.760000000002</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="5">
-        <v>46065</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3650</v>
+        <v>46184</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
       </c>
       <c r="D15" s="4">
         <v>200</v>
@@ -1508,20 +1521,20 @@
         <v>0</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="0"/>
-        <v>5242.2800000000007</v>
+        <f>I14+C15-E15-F15-G15-H15</f>
+        <v>12869.28</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J14-F15</f>
+        <v>12000</v>
       </c>
       <c r="K15" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K14-H15</f>
+        <v>0</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="3"/>
-        <v>10140.5</v>
+        <f>L14-G15+D15</f>
+        <v>25948.04</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -1530,8 +1543,8 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="6">
-        <f t="shared" si="5"/>
-        <v>5242.2800000000007</v>
+        <f>I15</f>
+        <v>12869.28</v>
       </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -1539,10 +1552,10 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="5">
-        <v>46072</v>
+        <v>46191</v>
       </c>
       <c r="C16" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D16" s="4">
         <v>200</v>
@@ -1560,32 +1573,30 @@
         <v>0</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="0"/>
-        <v>5242.2800000000007</v>
+        <f>I15+C16-E16-F16-G16-H16</f>
+        <v>16719.28</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J15-F16</f>
+        <v>12000</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K15-H16</f>
+        <v>0</v>
       </c>
       <c r="L16" s="6">
-        <f t="shared" si="3"/>
-        <v>10340.5</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>7</v>
-      </c>
+        <f>L15-G16+D16</f>
+        <v>26148.04</v>
+      </c>
+      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="6">
-        <f t="shared" si="5"/>
-        <v>5242.2800000000007</v>
+        <f>I16</f>
+        <v>16719.28</v>
       </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
@@ -1593,16 +1604,16 @@
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="5">
-        <v>46076</v>
+        <v>46198</v>
       </c>
       <c r="C17" s="3">
         <v>0</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>1760</v>
+        <v>200</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -1614,32 +1625,42 @@
         <v>0</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="0"/>
-        <v>3482.2800000000007</v>
+        <f>I16+C17-E17-F17-G17-H17</f>
+        <v>16719.28</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J16-F17</f>
+        <v>12000</v>
       </c>
       <c r="K17" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K16-H17</f>
+        <v>0</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="3"/>
-        <v>10340.5</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <f>L16-G17+D17</f>
+        <v>26348.04</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="18">
+        <f>N13</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <f>SUM(D14:D18)</f>
+        <v>800</v>
+      </c>
       <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
+      <c r="Q17" s="19">
+        <f>Q13</f>
+        <v>12000</v>
+      </c>
+      <c r="R17" s="24">
+        <f>R13+O12</f>
+        <v>25550.04</v>
+      </c>
       <c r="S17" s="6">
-        <f t="shared" si="5"/>
-        <v>3482.2800000000007</v>
+        <f>I17</f>
+        <v>16719.28</v>
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
@@ -1647,16 +1668,16 @@
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="5">
-        <v>46079</v>
+        <v>46203</v>
       </c>
       <c r="C18" s="3">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
-        <v>200</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1938</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1668,59 +1689,56 @@
         <v>0</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="0"/>
-        <v>7132.2800000000007</v>
+        <f>I17+C18-E18-F18-G18-H18</f>
+        <v>14781.279999999999</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J17-F18</f>
+        <v>12000</v>
       </c>
       <c r="K18" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K17-H18</f>
+        <v>0</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="3"/>
-        <v>10540.5</v>
+        <f>L17-G18+D18</f>
+        <v>26348.04</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="N18" s="19">
-        <f>N14</f>
-        <v>2548.89</v>
-      </c>
-      <c r="O18" s="4">
-        <f>SUM(D13:D18)</f>
-        <v>1000</v>
-      </c>
+      <c r="N18" s="18">
+        <f>N17-H13</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" s="2"/>
-      <c r="Q18" s="16">
-        <f>Q14</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="11">
-        <f>R14+O13</f>
-        <v>18540.5</v>
+      <c r="Q18" s="24">
+        <f>Q17-F15</f>
+        <v>12000</v>
+      </c>
+      <c r="R18" s="24">
+        <f>R17-G15</f>
+        <v>25550.04</v>
       </c>
       <c r="S18" s="6">
-        <f t="shared" si="5"/>
-        <v>7132.2800000000007</v>
+        <f>I18</f>
+        <v>14781.279999999999</v>
       </c>
       <c r="T18" s="10">
-        <f>N18+Q18+R18</f>
-        <v>21089.39</v>
+        <f>N17+Q17+R17</f>
+        <v>37550.04</v>
       </c>
       <c r="U18" s="14">
         <f>S17-T18</f>
-        <v>-17607.11</v>
+        <v>-20830.760000000002</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="5">
-        <v>46086</v>
+        <v>46205</v>
       </c>
       <c r="C19" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D19" s="4">
         <v>200</v>
@@ -1732,64 +1750,53 @@
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="0"/>
-        <v>2132.2800000000007</v>
+        <f>I18+C19-E19-F19-G19-H19</f>
+        <v>18631.28</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J18-F19</f>
+        <v>12000</v>
       </c>
       <c r="K19" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K18-H19</f>
+        <v>0</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" si="3"/>
-        <v>5740.5</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="19">
-        <f>N18-H13</f>
-        <v>2548.89</v>
-      </c>
+        <f>L18-G19+D19</f>
+        <v>26548.04</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
-      <c r="Q19" s="16">
-        <f>Q18-F19</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="11">
-        <f>R18-G18</f>
-        <v>18540.5</v>
-      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
       <c r="S19" s="6">
-        <f t="shared" si="5"/>
-        <v>2132.2800000000007</v>
+        <f>I19</f>
+        <v>18631.28</v>
       </c>
       <c r="T19" s="10">
-        <f>N19+Q19+R19</f>
-        <v>21089.39</v>
+        <f>N18+Q18+R18</f>
+        <v>37550.04</v>
       </c>
       <c r="U19" s="14">
         <f>S19-T19</f>
-        <v>-18957.11</v>
+        <v>-18918.760000000002</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="5">
-        <v>46093</v>
+        <v>46212</v>
       </c>
       <c r="C20" s="3">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <v>200</v>
@@ -1807,30 +1814,30 @@
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="0"/>
-        <v>5782.2800000000007</v>
+        <f>I19+C20-E20-F20-G20-H20</f>
+        <v>18631.28</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J19-F20</f>
+        <v>12000</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K19-H20</f>
+        <v>0</v>
       </c>
       <c r="L20" s="6">
-        <f t="shared" si="3"/>
-        <v>5940.5</v>
-      </c>
-      <c r="M20" s="2"/>
+        <f>L19-G20+D20</f>
+        <v>26748.04</v>
+      </c>
+      <c r="M20" s="5"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="6">
-        <f t="shared" si="5"/>
-        <v>5782.2800000000007</v>
+        <f>I20</f>
+        <v>18631.28</v>
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
@@ -1838,10 +1845,10 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="5">
-        <v>46100</v>
+        <v>46219</v>
       </c>
       <c r="C21" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D21" s="4">
         <v>200</v>
@@ -1859,32 +1866,30 @@
         <v>0</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="0"/>
-        <v>5782.2800000000007</v>
+        <f>I20+C21-E21-F21-G21-H21</f>
+        <v>22481.279999999999</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J20-F21</f>
+        <v>12000</v>
       </c>
       <c r="K21" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K20-H21</f>
+        <v>0</v>
       </c>
       <c r="L21" s="6">
-        <f t="shared" si="3"/>
-        <v>6140.5</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>18</v>
-      </c>
+        <f>L20-G21+D21</f>
+        <v>26948.04</v>
+      </c>
+      <c r="M21" s="5"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="6">
-        <f t="shared" si="5"/>
-        <v>5782.2800000000007</v>
+        <f>I21</f>
+        <v>22481.279999999999</v>
       </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
@@ -1892,13 +1897,13 @@
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="5">
-        <v>46104</v>
+        <v>46226</v>
       </c>
       <c r="C22" s="3">
-        <v>3650</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1913,30 +1918,42 @@
         <v>0</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="0"/>
-        <v>9432.2800000000007</v>
+        <f>I21+C22-E22-F22-G22-H22</f>
+        <v>22481.279999999999</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J21-F22</f>
+        <v>12000</v>
       </c>
       <c r="K22" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K21-H22</f>
+        <v>0</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="3"/>
-        <v>6140.5</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <f>L21-G22+D22</f>
+        <v>27148.04</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="18">
+        <f>N18</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <f>SUM(D19:D23)</f>
+        <v>1000</v>
+      </c>
       <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
+      <c r="Q22" s="21">
+        <f>Q18</f>
+        <v>12000</v>
+      </c>
+      <c r="R22" s="27">
+        <f>R18+O17</f>
+        <v>26350.04</v>
+      </c>
       <c r="S22" s="6">
-        <f t="shared" si="5"/>
-        <v>9432.2800000000007</v>
+        <f>I22</f>
+        <v>22481.279999999999</v>
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
@@ -1944,16 +1961,16 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="5">
-        <v>46107</v>
+        <v>46233</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="D23" s="4">
         <v>200</v>
       </c>
       <c r="E23" s="4">
-        <v>1760</v>
+        <v>1938</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -1965,30 +1982,39 @@
         <v>0</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="0"/>
-        <v>7672.2800000000007</v>
+        <f>I22+C23-E23-F23-G23-H23</f>
+        <v>24393.279999999999</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J22-F23</f>
+        <v>12000</v>
       </c>
       <c r="K23" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K22-H23</f>
+        <v>0</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="3"/>
-        <v>6340.5</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <f>L22-G23+D23</f>
+        <v>27348.04</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="18">
+        <f>N22-H23</f>
+        <v>0</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
+      <c r="Q23" s="27">
+        <f>Q22-F20</f>
+        <v>12000</v>
+      </c>
+      <c r="R23" s="27">
+        <f>R22-G20</f>
+        <v>26350.04</v>
+      </c>
       <c r="S23" s="6">
-        <f t="shared" si="5"/>
-        <v>7672.2800000000007</v>
+        <f>I23</f>
+        <v>24393.279999999999</v>
       </c>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
@@ -1996,7 +2022,7 @@
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="5">
-        <v>46114</v>
+        <v>46240</v>
       </c>
       <c r="C24" s="3">
         <v>0</v>
@@ -2011,182 +2037,322 @@
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>3557.76</v>
+        <v>0</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="0"/>
-        <v>4114.5200000000004</v>
+        <f>I23+C24-E24-F24-G24-H24</f>
+        <v>24393.279999999999</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>J23-F24</f>
+        <v>12000</v>
       </c>
       <c r="K24" s="15">
-        <f t="shared" si="2"/>
-        <v>1618.9700000000003</v>
+        <f>K23-H24</f>
+        <v>0</v>
       </c>
       <c r="L24" s="6">
-        <f t="shared" si="3"/>
-        <v>2982.74</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="19">
-        <f>N19</f>
-        <v>2548.89</v>
-      </c>
-      <c r="O24" s="4">
-        <f>SUM(D19:D23)</f>
-        <v>800</v>
-      </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="16">
-        <f>Q19</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="11">
-        <f>R19+O18</f>
-        <v>19540.5</v>
-      </c>
+        <f>L23-G24+D24</f>
+        <v>27548.04</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
       <c r="S24" s="6">
-        <f t="shared" si="5"/>
-        <v>4114.5200000000004</v>
-      </c>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
+        <f>I24</f>
+        <v>24393.279999999999</v>
+      </c>
+      <c r="T24" s="10">
+        <f>N23+Q23+R23</f>
+        <v>38350.04</v>
+      </c>
+      <c r="U24" s="14">
+        <f>S23-T24</f>
+        <v>-13956.760000000002</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="B25" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3850</v>
+      </c>
+      <c r="D25" s="4">
+        <v>200</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <f>I24+C25-E25-F25-G25-H25</f>
+        <v>28243.279999999999</v>
+      </c>
+      <c r="J25" s="15">
+        <f>J24-F25</f>
+        <v>12000</v>
+      </c>
+      <c r="K25" s="15">
+        <f>K24-H25</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="6">
+        <f>L24-G25+D25</f>
+        <v>27748.04</v>
+      </c>
       <c r="M25" s="5"/>
-      <c r="N25" s="19">
-        <f>N24-H23</f>
-        <v>2548.89</v>
-      </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="16">
-        <f>Q24-F23</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="11">
-        <f>R24-G23</f>
-        <v>19540.5</v>
-      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
       <c r="S25" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
+        <f>I25</f>
+        <v>28243.279999999999</v>
+      </c>
+      <c r="T25" s="10">
+        <f>N24+Q24+R24</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="14">
+        <f>S25-T25</f>
+        <v>28243.279999999999</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
+      <c r="B26" s="5">
+        <v>46254</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>200</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6">
+        <f>I25+C26-E26-F26-G26-H26</f>
+        <v>28243.279999999999</v>
+      </c>
+      <c r="J26" s="15">
+        <f>J25-F26</f>
+        <v>12000</v>
+      </c>
+      <c r="K26" s="15">
+        <f>K25-H26</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
+        <f>L25-G26+D26</f>
+        <v>27948.04</v>
+      </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
+      <c r="S26" s="6">
+        <f>I26</f>
+        <v>28243.279999999999</v>
+      </c>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="B27" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3850</v>
+      </c>
+      <c r="D27" s="4">
+        <v>200</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
+        <f>I26+C27-E27-F27-G27-H27</f>
+        <v>32093.279999999999</v>
+      </c>
+      <c r="J27" s="15">
+        <f>J26-F27</f>
+        <v>12000</v>
+      </c>
+      <c r="K27" s="15">
+        <f>K26-H27</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="6">
+        <f>L26-G27+D27</f>
+        <v>28148.04</v>
+      </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
+      <c r="S27" s="6">
+        <f>I27</f>
+        <v>32093.279999999999</v>
+      </c>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="B28" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>200</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6">
+        <f>I27+C28-E28-F28-G28-H28</f>
+        <v>32093.279999999999</v>
+      </c>
+      <c r="J28" s="15">
+        <f>J27-F28</f>
+        <v>12000</v>
+      </c>
+      <c r="K28" s="15">
+        <f>K27-H28</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="6">
+        <f>L27-G28+D28</f>
+        <v>28348.04</v>
+      </c>
       <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
+      <c r="N28" s="18">
+        <f>N23</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="4">
+        <f>SUM(D24:D27)</f>
+        <v>800</v>
+      </c>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="27">
+        <f>Q23</f>
+        <v>12000</v>
+      </c>
+      <c r="R28" s="27">
+        <f>R23+O22</f>
+        <v>27350.04</v>
+      </c>
+      <c r="S28" s="6">
+        <f>I28</f>
+        <v>32093.279999999999</v>
+      </c>
+      <c r="T28" s="10">
+        <f>N28+Q28+R28</f>
+        <v>39350.04</v>
+      </c>
+      <c r="U28" s="14">
+        <f>S28-T28</f>
+        <v>-7256.760000000002</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="18">
+        <f>N28-H28</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="27">
+        <f>Q28-F28</f>
+        <v>12000</v>
+      </c>
+      <c r="R29" s="27">
+        <f>R28-G25</f>
+        <v>27350.04</v>
+      </c>
+      <c r="S29" s="6">
+        <f>I29</f>
+        <v>0</v>
+      </c>
+      <c r="T29" s="10">
+        <f>N29+Q29+R29</f>
+        <v>39350.04</v>
+      </c>
+      <c r="U29" s="14">
+        <f>S30-T29</f>
+        <v>-39350.04</v>
+      </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
-      <c r="B30" s="5"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2198,18 +2364,166 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="6"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="R31" s="21"/>
-      <c r="S31" s="20"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N37" s="30"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="22"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q38" s="23"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q39" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
